--- a/output/laminas_comunales/comunal_m_saldomigr_a_2023_o_higgins.xlsx
+++ b/output/laminas_comunales/comunal_m_saldomigr_a_2023_o_higgins.xlsx
@@ -1095,7 +1095,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Periodo 2019-2023. Escala de colores estandarizada a nivel nacional para todo el periodo.</t>
+          <t>Periodo 2019-2023. Escala comunal recortada a percentiles 3-97. Bajo umbral: Rancagua (-9.171).</t>
         </is>
       </c>
     </row>
